--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N75_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0001T0006Z000C1N75_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.60670274255019</v>
+        <v>3.511089195664406</v>
       </c>
       <c r="D2" t="n">
-        <v>21.68523805648192</v>
+        <v>3.523851184178312</v>
       </c>
       <c r="E2" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F2" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>55.62035321121235</v>
+        <v>9.038307396822006</v>
       </c>
       <c r="D3" t="n">
-        <v>55.37701425371106</v>
+        <v>8.998764816228048</v>
       </c>
       <c r="E3" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F3" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.55128389640918</v>
+        <v>1.552083633166492</v>
       </c>
       <c r="D4" t="n">
-        <v>9.86121128764545</v>
+        <v>1.602446834242386</v>
       </c>
       <c r="E4" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F4" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.28108290316129</v>
+        <v>6.70817597176371</v>
       </c>
       <c r="D5" t="n">
-        <v>40.86167815120414</v>
+        <v>6.640022699570673</v>
       </c>
       <c r="E5" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F5" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>15.60670653313899</v>
+        <v>2.536089811635086</v>
       </c>
       <c r="D6" t="n">
-        <v>15.23911893905862</v>
+        <v>2.476356827597026</v>
       </c>
       <c r="E6" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F6" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.95593283880572</v>
+        <v>5.192839086305929</v>
       </c>
       <c r="D7" t="n">
-        <v>31.53126943358314</v>
+        <v>5.12383128295726</v>
       </c>
       <c r="E7" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F7" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>20.24791675805566</v>
+        <v>3.290286473184045</v>
       </c>
       <c r="D8" t="n">
-        <v>19.83197178537031</v>
+        <v>3.222695415122676</v>
       </c>
       <c r="E8" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F8" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.81108243153593</v>
+        <v>2.081800895124588</v>
       </c>
       <c r="D9" t="n">
-        <v>13.13946323853389</v>
+        <v>2.135162776261758</v>
       </c>
       <c r="E9" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F9" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>30.31871617346925</v>
+        <v>4.926791378188753</v>
       </c>
       <c r="D10" t="n">
-        <v>30.31990838659976</v>
+        <v>4.926985112822462</v>
       </c>
       <c r="E10" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F10" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90977077140393</v>
+        <v>3.23533775035314</v>
       </c>
       <c r="D11" t="n">
-        <v>19.92145852999598</v>
+        <v>3.237237011124347</v>
       </c>
       <c r="E11" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F11" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>18.14155105847667</v>
+        <v>2.948002047002458</v>
       </c>
       <c r="D12" t="n">
-        <v>18.3828364429653</v>
+        <v>2.987210921981862</v>
       </c>
       <c r="E12" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F12" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>22.8723935147629</v>
+        <v>3.716763946148971</v>
       </c>
       <c r="D13" t="n">
-        <v>23.10477249874659</v>
+        <v>3.754525531046322</v>
       </c>
       <c r="E13" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F13" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>41.96830920853636</v>
+        <v>6.819850246387159</v>
       </c>
       <c r="D14" t="n">
-        <v>42.09940144589056</v>
+        <v>6.841152734957216</v>
       </c>
       <c r="E14" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F14" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>17.0045152213821</v>
+        <v>2.763233723474592</v>
       </c>
       <c r="D15" t="n">
-        <v>17.45448974356188</v>
+        <v>2.836354583328805</v>
       </c>
       <c r="E15" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F15" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>46.65380373072274</v>
+        <v>7.581243106242446</v>
       </c>
       <c r="D16" t="n">
-        <v>46.48576219008638</v>
+        <v>7.553936355889037</v>
       </c>
       <c r="E16" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F16" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>5.428540353100834</v>
+        <v>0.8821378073788855</v>
       </c>
       <c r="D17" t="n">
-        <v>1.789384392960965</v>
+        <v>0.2907749638561568</v>
       </c>
       <c r="E17" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F17" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>46.01931942790203</v>
+        <v>7.478139407034081</v>
       </c>
       <c r="D18" t="n">
-        <v>46.24904153650065</v>
+        <v>7.515469249681356</v>
       </c>
       <c r="E18" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F18" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>7.949311627894505</v>
+        <v>1.291763139532857</v>
       </c>
       <c r="D19" t="n">
-        <v>9.305134105484145</v>
+        <v>1.512084292141174</v>
       </c>
       <c r="E19" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F19" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>4.525060684322188</v>
+        <v>0.7353223612023556</v>
       </c>
       <c r="D20" t="n">
-        <v>3.970701876721539</v>
+        <v>0.64523905496725</v>
       </c>
       <c r="E20" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F20" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>17.70765537720114</v>
+        <v>2.877493998795185</v>
       </c>
       <c r="D21" t="n">
-        <v>17.13734587118194</v>
+        <v>2.784818704067065</v>
       </c>
       <c r="E21" t="n">
-        <v>14.60632447073039</v>
+        <v>2.373527726493689</v>
       </c>
       <c r="F21" t="n">
-        <v>14.76431814201525</v>
+        <v>2.399201698077479</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
